--- a/2025/0727_이씨마이너_입사서류/7.인사기록카드.xlsx
+++ b/2025/0727_이씨마이너_입사서류/7.인사기록카드.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\travail\2025\0727_이씨마이너_입사서류\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DF0E77-4B2B-4CF5-BC0C-E1BACE1B40DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0E86B1-B113-46F2-AC81-10780F4605DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0C12F17-5128-49A8-8E87-65E98ED01554}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="88">
   <si>
     <t>인 사 기 록  카 드</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -135,18 +135,8 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>010-0000-0000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>모</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-0000-0001</t>
-  </si>
-  <si>
-    <t>010-0000-0002</t>
   </si>
   <si>
     <t>학력</t>
@@ -199,14 +189,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>친구</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>직장상사</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>㈜이씨마이너</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -343,10 +325,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>자(姊, 누나)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>010-8791-7290</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -356,6 +334,50 @@
   </si>
   <si>
     <t>컨설팅본부</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>누나</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>허남윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오산대학교</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-6437-2204</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>황성하</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>약사</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-2779-0216</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오승상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도교수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>친척어른(사촌)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-4401-5001</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -828,7 +850,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -874,9 +896,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -907,19 +926,100 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -928,59 +1028,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1003,27 +1058,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1041,39 +1084,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1402,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE24BBAF-23B0-450E-95CB-B35B3766356D}">
-  <dimension ref="A2:K48"/>
+  <dimension ref="A2:K45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.125" style="1" customWidth="1"/>
@@ -1417,18 +1427,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="28.5" x14ac:dyDescent="0.3">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
     </row>
     <row r="3" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D3" s="2"/>
@@ -1438,22 +1448,22 @@
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="2:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
       <c r="J4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1469,101 +1479,99 @@
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="2:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="47"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="40"/>
       <c r="J6" s="6" t="s">
         <v>5</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="42"/>
-      <c r="C7" s="30" t="s">
+      <c r="B7" s="35"/>
+      <c r="C7" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="50"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="44"/>
       <c r="J7" s="8" t="s">
         <v>7</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="42"/>
-      <c r="C8" s="26" t="s">
+      <c r="B8" s="35"/>
+      <c r="C8" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="29"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="56"/>
       <c r="J8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>57</v>
-      </c>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="42"/>
-      <c r="C9" s="30" t="s">
+      <c r="B9" s="35"/>
+      <c r="C9" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="32"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="43"/>
-      <c r="C10" s="33" t="s">
+      <c r="B10" s="36"/>
+      <c r="C10" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="36"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="59"/>
       <c r="J10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>59</v>
+      <c r="K10" s="20" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="2:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1579,56 +1587,56 @@
       <c r="K11" s="5"/>
     </row>
     <row r="12" spans="2:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="55" t="s">
+      <c r="D12" s="65"/>
+      <c r="E12" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="58" t="s">
-        <v>62</v>
+      <c r="K12" s="47" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="52"/>
-      <c r="C13" s="30" t="s">
+      <c r="B13" s="63"/>
+      <c r="C13" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="59"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="48"/>
     </row>
     <row r="14" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="53"/>
-      <c r="C14" s="33" t="s">
+      <c r="B14" s="64"/>
+      <c r="C14" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="60"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="49"/>
     </row>
     <row r="15" spans="2:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="14"/>
@@ -1637,538 +1645,486 @@
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="2:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54" t="s">
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="54"/>
-      <c r="I16" s="44" t="s">
+      <c r="G16" s="65"/>
+      <c r="I16" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="J16" s="37"/>
+      <c r="K16" s="18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B17" s="63"/>
+      <c r="C17" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="61"/>
+      <c r="I17" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="J17" s="60"/>
+      <c r="K17" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="63"/>
+      <c r="C18" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="61" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="61"/>
+      <c r="I18" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18" s="60"/>
+      <c r="K18" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="63"/>
+      <c r="C19" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" s="61"/>
+      <c r="I19" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="J19" s="60"/>
+      <c r="K19" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="64"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="16"/>
+    </row>
+    <row r="21" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="17"/>
+      <c r="B22" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="73"/>
+    </row>
+    <row r="23" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="63"/>
+      <c r="C23" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="K23" s="46"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B24" s="63"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="K24" s="79"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="71"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="26"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B26" s="71"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="26"/>
+    </row>
+    <row r="27" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="64"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="23"/>
+    </row>
+    <row r="28" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="65"/>
+      <c r="I29" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="J29" s="37"/>
+      <c r="K29" s="18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="63"/>
+      <c r="C30" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" s="61"/>
+      <c r="I30" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="J30" s="60"/>
+      <c r="K30" s="19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B31" s="63"/>
+      <c r="C31" s="60" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="61"/>
+      <c r="I31" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="J31" s="60"/>
+      <c r="K31" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="64"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="19"/>
+    </row>
+    <row r="33" spans="2:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="2:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" s="65"/>
+      <c r="I34" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="J34" s="37"/>
+      <c r="K34" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35" s="63"/>
+      <c r="C35" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="61"/>
+      <c r="I35" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" s="60"/>
+      <c r="K35" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B36" s="63"/>
+      <c r="C36" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="G36" s="61"/>
+      <c r="I36" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="J16" s="44"/>
-      <c r="K16" s="19" t="s">
+      <c r="J36" s="60"/>
+      <c r="K36" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="63"/>
+      <c r="C37" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="G37" s="61"/>
+      <c r="I37" s="60" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="52"/>
-      <c r="C17" s="61" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="62" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" s="62"/>
-      <c r="I17" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" s="61"/>
-      <c r="K17" s="16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="52"/>
-      <c r="C18" s="61" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="62" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="62"/>
-      <c r="I18" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="J18" s="61"/>
-      <c r="K18" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="52"/>
-      <c r="C19" s="61" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="62" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="62"/>
-      <c r="I19" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="J19" s="61"/>
-      <c r="K19" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="52"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="16"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="52"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="16"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="52"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="16"/>
-    </row>
-    <row r="23" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="53"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="17"/>
-    </row>
-    <row r="24" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="1:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" s="66"/>
-    </row>
-    <row r="26" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="52"/>
-      <c r="C26" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="K26" s="81"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B27" s="52"/>
-      <c r="C27" s="74"/>
-      <c r="D27" s="75"/>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="82" t="s">
-        <v>76</v>
-      </c>
-      <c r="K27" s="83"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B28" s="52"/>
-      <c r="C28" s="74"/>
-      <c r="D28" s="75"/>
-      <c r="E28" s="75"/>
-      <c r="F28" s="75"/>
-      <c r="G28" s="75"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="25"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B29" s="52"/>
-      <c r="C29" s="74"/>
-      <c r="D29" s="75"/>
-      <c r="E29" s="75"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="76"/>
-      <c r="I29" s="69"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="25"/>
-    </row>
-    <row r="30" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="53"/>
-      <c r="C30" s="77"/>
-      <c r="D30" s="78"/>
-      <c r="E30" s="78"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="78"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="24"/>
-    </row>
-    <row r="31" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="1:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" s="54" t="s">
+      <c r="J37" s="60"/>
+      <c r="K37" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B38" s="63"/>
+      <c r="C38" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="61"/>
+      <c r="I38" s="60"/>
+      <c r="J38" s="60"/>
+      <c r="K38" s="19"/>
+    </row>
+    <row r="39" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="2:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="80" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54" t="s">
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40" s="65"/>
+      <c r="I40" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="G32" s="54"/>
-      <c r="I32" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="J32" s="44"/>
-      <c r="K32" s="19" t="s">
+      <c r="J40" s="37"/>
+      <c r="K40" s="18" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B33" s="52"/>
-      <c r="C33" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="G33" s="62"/>
-      <c r="I33" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="J33" s="61"/>
-      <c r="K33" s="20" t="s">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B41" s="81"/>
+      <c r="C41" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="60"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="61"/>
+      <c r="I41" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="J41" s="60"/>
+      <c r="K41" s="19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B42" s="81"/>
+      <c r="C42" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="G42" s="61"/>
+      <c r="I42" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="J42" s="60"/>
+      <c r="K42" s="19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B34" s="52"/>
-      <c r="C34" s="61" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="62" t="s">
-        <v>79</v>
-      </c>
-      <c r="G34" s="62"/>
-      <c r="I34" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" s="61"/>
-      <c r="K34" s="20" t="s">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B43" s="81"/>
+      <c r="C43" s="60" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B35" s="52"/>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="I35" s="61"/>
-      <c r="J35" s="61"/>
-      <c r="K35" s="20"/>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B36" s="52"/>
-      <c r="C36" s="61"/>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="62"/>
-      <c r="G36" s="62"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="20"/>
-    </row>
-    <row r="37" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="53"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="64"/>
-      <c r="I37" s="63"/>
-      <c r="J37" s="63"/>
-      <c r="K37" s="20"/>
-    </row>
-    <row r="38" spans="2:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="2:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54"/>
-      <c r="F39" s="54" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="54"/>
-      <c r="I39" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="J39" s="44"/>
-      <c r="K39" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="52"/>
-      <c r="C40" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="62" t="s">
-        <v>49</v>
-      </c>
-      <c r="G40" s="62"/>
-      <c r="I40" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="J40" s="61"/>
-      <c r="K40" s="20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="52"/>
-      <c r="C41" s="61" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="62" t="s">
-        <v>50</v>
-      </c>
-      <c r="G41" s="62"/>
-      <c r="I41" s="61" t="s">
-        <v>51</v>
-      </c>
-      <c r="J41" s="61"/>
-      <c r="K41" s="20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B42" s="52"/>
-      <c r="C42" s="61" t="s">
+      <c r="D43" s="60"/>
+      <c r="E43" s="60"/>
+      <c r="F43" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="G43" s="61"/>
+      <c r="I43" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="62" t="s">
-        <v>50</v>
-      </c>
-      <c r="G42" s="62"/>
-      <c r="I42" s="61" t="s">
-        <v>52</v>
-      </c>
-      <c r="J42" s="61"/>
-      <c r="K42" s="20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B43" s="52"/>
-      <c r="C43" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="D43" s="61"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="62"/>
-      <c r="G43" s="62"/>
-      <c r="I43" s="61"/>
-      <c r="J43" s="61"/>
-      <c r="K43" s="20"/>
-    </row>
-    <row r="44" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="2:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" s="54"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G45" s="54"/>
-      <c r="I45" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="J45" s="44"/>
-      <c r="K45" s="15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B46" s="85"/>
-      <c r="C46" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" s="61"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="62"/>
-      <c r="I46" s="61" t="s">
-        <v>42</v>
-      </c>
-      <c r="J46" s="61"/>
-      <c r="K46" s="20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B47" s="85"/>
-      <c r="C47" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="D47" s="61"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="G47" s="62"/>
-      <c r="I47" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="J47" s="61"/>
-      <c r="K47" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B48" s="85"/>
-      <c r="C48" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="G48" s="62"/>
-      <c r="I48" s="61" t="s">
-        <v>44</v>
-      </c>
-      <c r="J48" s="61"/>
-      <c r="K48" s="20" t="s">
-        <v>30</v>
-      </c>
+      <c r="J43" s="60"/>
+      <c r="K43" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C45" s="60"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="60"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="61"/>
+      <c r="I45" s="60"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="103">
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="B39:B43"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="I39:J39"/>
+  <mergeCells count="91">
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B40:B43"/>
     <mergeCell ref="C40:E40"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="I40:J40"/>
-    <mergeCell ref="B45:B48"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="I46:J46"/>
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="F41:G41"/>
     <mergeCell ref="I41:J41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="I34:J34"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="C36:E36"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="I36:J36"/>
-    <mergeCell ref="B32:B37"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="I31:J31"/>
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="I32:J32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="I25:I30"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="C26:H30"/>
-    <mergeCell ref="B16:B23"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="I22:I27"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B16:B20"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="I16:J16"/>
@@ -2178,35 +2134,24 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="I18:J18"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J24:K24"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E12:I12"/>
     <mergeCell ref="J12:J14"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="C23:G23"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:I14"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:K9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:J19"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:H4"/>
@@ -2215,6 +2160,12 @@
     <mergeCell ref="E6:I6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:I7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:K9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:I10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>

--- a/2025/0727_이씨마이너_입사서류/7.인사기록카드.xlsx
+++ b/2025/0727_이씨마이너_입사서류/7.인사기록카드.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\travail\2025\0727_이씨마이너_입사서류\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\travail\2025\0727_이씨마이너_입사서류\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DF0E77-4B2B-4CF5-BC0C-E1BACE1B40DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2859A527-CAA9-4032-B3A3-09F2C28F4D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0C12F17-5128-49A8-8E87-65E98ED01554}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0C12F17-5128-49A8-8E87-65E98ED01554}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="82">
   <si>
     <t>인 사 기 록  카 드</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -135,20 +135,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>010-0000-0000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>모</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>010-0000-0001</t>
-  </si>
-  <si>
-    <t>010-0000-0002</t>
-  </si>
-  <si>
     <t>학력</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -169,10 +159,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>헤딩없음</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>졸업</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -182,10 +168,6 @@
   </si>
   <si>
     <t>대학원 석사</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>대학원 박사</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -195,18 +177,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>지인</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>친구</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>직장상사</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>㈜이씨마이너</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -343,10 +313,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>자(姊, 누나)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>010-8791-7290</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -356,6 +322,38 @@
   </si>
   <si>
     <t>컨설팅본부</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오승상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도교수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-4401-5001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>허남윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오산대학교</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>친척(사촌)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-6437-2204</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>누나</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -442,7 +440,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -819,6 +817,84 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="double">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="double">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="double">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="double">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -828,7 +904,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -874,9 +950,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -907,19 +980,79 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -928,58 +1061,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1003,21 +1091,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1082,10 +1155,34 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1402,61 +1499,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE24BBAF-23B0-450E-95CB-B35B3766356D}">
-  <dimension ref="A2:K48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:K45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="3.625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="3.625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="0.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="3.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="26.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="1.09765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="3.59765625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="3.59765625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="13.59765625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="0.8984375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="3.59765625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.59765625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="26.59765625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="28.5" x14ac:dyDescent="0.3">
-      <c r="B2" s="37" t="s">
+    <row r="2" spans="2:11" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-    </row>
-    <row r="3" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+    </row>
+    <row r="3" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="2:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="38" t="s">
+    <row r="4" spans="2:11" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
       <c r="J4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1468,105 +1565,103 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="2:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="42" t="s">
+    <row r="6" spans="2:11" ht="18" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="47"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="35"/>
       <c r="J6" s="6" t="s">
         <v>5</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="42"/>
-      <c r="C7" s="30" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B7" s="30"/>
+      <c r="C7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="50"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="39"/>
       <c r="J7" s="8" t="s">
         <v>7</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="42"/>
-      <c r="C8" s="26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B8" s="30"/>
+      <c r="C8" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="29"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="49"/>
       <c r="J8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="42"/>
-      <c r="C9" s="30" t="s">
+      <c r="K8" s="11"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B9" s="30"/>
+      <c r="C9" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="32"/>
-    </row>
-    <row r="10" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="43"/>
-      <c r="C10" s="33" t="s">
+      <c r="D9" s="36"/>
+      <c r="E9" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="50"/>
+      <c r="K9" s="51"/>
+    </row>
+    <row r="10" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="31"/>
+      <c r="C10" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="36"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="52"/>
       <c r="J10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K10" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -1578,576 +1673,511 @@
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="2:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="51" t="s">
+    <row r="12" spans="2:11" ht="18" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="55" t="s">
+      <c r="D12" s="58"/>
+      <c r="E12" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="58" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="52"/>
-      <c r="C13" s="30" t="s">
+      <c r="K12" s="40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B13" s="56"/>
+      <c r="C13" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="59"/>
-    </row>
-    <row r="14" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="53"/>
-      <c r="C14" s="33" t="s">
+      <c r="D13" s="36"/>
+      <c r="E13" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="41"/>
+    </row>
+    <row r="14" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="57"/>
+      <c r="C14" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="60"/>
-    </row>
-    <row r="15" spans="2:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D14" s="45"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="42"/>
+    </row>
+    <row r="15" spans="2:11" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B15" s="14"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="2:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="51" t="s">
+    <row r="16" spans="2:11" ht="18" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54" t="s">
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="54"/>
-      <c r="I16" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="44"/>
-      <c r="K16" s="19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="52"/>
-      <c r="C17" s="61" t="s">
+      <c r="G16" s="58"/>
+      <c r="I16" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" s="32"/>
+      <c r="K16" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B17" s="56"/>
+      <c r="C17" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" s="53"/>
+      <c r="I17" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" s="54"/>
+      <c r="K17" s="19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B18" s="56"/>
+      <c r="C18" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="53"/>
+      <c r="I18" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="J18" s="54"/>
+      <c r="K18" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B19" s="56"/>
+      <c r="C19" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="62" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" s="62"/>
-      <c r="I17" s="61" t="s">
+      <c r="G19" s="53"/>
+      <c r="I19" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" s="54"/>
+      <c r="K19" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B20" s="56"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
+      <c r="K20" s="15"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B21" s="56"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="15"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B22" s="56"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="15"/>
+    </row>
+    <row r="23" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="57"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="16"/>
+    </row>
+    <row r="24" spans="1:11" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="25" spans="1:11" ht="18" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="17"/>
+      <c r="B25" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="65"/>
+    </row>
+    <row r="26" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="56"/>
+      <c r="C26" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="J17" s="61"/>
-      <c r="K17" s="16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="52"/>
-      <c r="C18" s="61" t="s">
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="62" t="s">
+      <c r="K26" s="80"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B27" s="56"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="G18" s="62"/>
-      <c r="I18" s="61" t="s">
+      <c r="K27" s="82"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B28" s="56"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="24"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B29" s="56"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="24"/>
+    </row>
+    <row r="30" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B30" s="57"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="78"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="23"/>
+    </row>
+    <row r="31" spans="1:11" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="32" spans="1:11" ht="18" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="58"/>
+      <c r="I32" s="84" t="s">
+        <v>40</v>
+      </c>
+      <c r="J32" s="84"/>
+      <c r="K32" s="85" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B33" s="56"/>
+      <c r="C33" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="I33" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33" s="54"/>
+      <c r="K33" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B34" s="56"/>
+      <c r="C34" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" s="53"/>
+      <c r="I34" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" s="54"/>
+      <c r="K34" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="J18" s="61"/>
-      <c r="K18" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="52"/>
-      <c r="C19" s="61" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="62" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="62"/>
-      <c r="I19" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="J19" s="61"/>
-      <c r="K19" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="52"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="16"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="52"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="16"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="52"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="16"/>
-    </row>
-    <row r="23" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="53"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="17"/>
-    </row>
-    <row r="24" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="1:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" s="66"/>
-    </row>
-    <row r="26" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="52"/>
-      <c r="C26" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="K26" s="81"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B27" s="52"/>
-      <c r="C27" s="74"/>
-      <c r="D27" s="75"/>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="82" t="s">
-        <v>76</v>
-      </c>
-      <c r="K27" s="83"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B28" s="52"/>
-      <c r="C28" s="74"/>
-      <c r="D28" s="75"/>
-      <c r="E28" s="75"/>
-      <c r="F28" s="75"/>
-      <c r="G28" s="75"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="25"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B29" s="52"/>
-      <c r="C29" s="74"/>
-      <c r="D29" s="75"/>
-      <c r="E29" s="75"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="76"/>
-      <c r="I29" s="69"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="25"/>
-    </row>
-    <row r="30" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="53"/>
-      <c r="C30" s="77"/>
-      <c r="D30" s="78"/>
-      <c r="E30" s="78"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="78"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="24"/>
-    </row>
-    <row r="31" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="1:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" s="54"/>
-      <c r="I32" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="J32" s="44"/>
-      <c r="K32" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B33" s="52"/>
-      <c r="C33" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="62" t="s">
+    </row>
+    <row r="35" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="57"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="I35" s="86"/>
+      <c r="J35" s="86"/>
+      <c r="K35" s="87"/>
+    </row>
+    <row r="36" spans="2:11" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="37" spans="2:11" ht="18" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="G33" s="62"/>
-      <c r="I33" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="J33" s="61"/>
-      <c r="K33" s="20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B34" s="52"/>
-      <c r="C34" s="61" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="62" t="s">
-        <v>79</v>
-      </c>
-      <c r="G34" s="62"/>
-      <c r="I34" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" s="61"/>
-      <c r="K34" s="20" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B35" s="52"/>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="I35" s="61"/>
-      <c r="J35" s="61"/>
-      <c r="K35" s="20"/>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B36" s="52"/>
-      <c r="C36" s="61"/>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="62"/>
-      <c r="G36" s="62"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="20"/>
-    </row>
-    <row r="37" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="53"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="64"/>
-      <c r="I37" s="63"/>
-      <c r="J37" s="63"/>
-      <c r="K37" s="20"/>
-    </row>
-    <row r="38" spans="2:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="2:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="51" t="s">
+      <c r="C37" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="58"/>
+      <c r="I37" s="84" t="s">
+        <v>30</v>
+      </c>
+      <c r="J37" s="84"/>
+      <c r="K37" s="85" t="s">
         <v>31</v>
       </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B38" s="56"/>
+      <c r="C38" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="91" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" s="91"/>
+      <c r="I38" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" s="54"/>
+      <c r="K38" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B39" s="56"/>
       <c r="C39" s="54" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D39" s="54"/>
       <c r="E39" s="54"/>
-      <c r="F39" s="54" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="54"/>
-      <c r="I39" s="44" t="s">
+      <c r="F39" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="G39" s="91"/>
+      <c r="I39" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="J39" s="54"/>
+      <c r="K39" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="J39" s="44"/>
-      <c r="K39" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="52"/>
-      <c r="C40" s="61" t="s">
+    </row>
+    <row r="40" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B40" s="57"/>
+      <c r="C40" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="62" t="s">
-        <v>49</v>
-      </c>
-      <c r="G40" s="62"/>
-      <c r="I40" s="61" t="s">
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="92" t="s">
+        <v>42</v>
+      </c>
+      <c r="G40" s="92"/>
+      <c r="I40" s="86" t="s">
+        <v>44</v>
+      </c>
+      <c r="J40" s="86"/>
+      <c r="K40" s="87" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="42" spans="2:11" ht="18" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="J40" s="61"/>
-      <c r="K40" s="20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="52"/>
-      <c r="C41" s="61" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="62" t="s">
-        <v>50</v>
-      </c>
-      <c r="G41" s="62"/>
-      <c r="I41" s="61" t="s">
-        <v>51</v>
-      </c>
-      <c r="J41" s="61"/>
-      <c r="K41" s="20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B42" s="52"/>
-      <c r="C42" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="62" t="s">
-        <v>50</v>
-      </c>
-      <c r="G42" s="62"/>
-      <c r="I42" s="61" t="s">
-        <v>52</v>
-      </c>
-      <c r="J42" s="61"/>
-      <c r="K42" s="20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B43" s="52"/>
-      <c r="C43" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="D43" s="61"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="62"/>
-      <c r="G43" s="62"/>
-      <c r="I43" s="61"/>
-      <c r="J43" s="61"/>
-      <c r="K43" s="20"/>
-    </row>
-    <row r="44" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="2:11" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="54" t="s">
+      <c r="C42" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="D45" s="54"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54" t="s">
+      <c r="D42" s="84"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="G45" s="54"/>
-      <c r="I45" s="44" t="s">
+      <c r="G42" s="84"/>
+      <c r="I42" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="J45" s="44"/>
-      <c r="K45" s="15" t="s">
+      <c r="J42" s="84"/>
+      <c r="K42" s="85" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B46" s="85"/>
-      <c r="C46" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" s="61"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="62"/>
-      <c r="I46" s="61" t="s">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B43" s="83"/>
+      <c r="C43" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="J46" s="61"/>
-      <c r="K46" s="20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B47" s="85"/>
-      <c r="C47" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="D47" s="61"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="G47" s="62"/>
-      <c r="I47" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="J47" s="61"/>
-      <c r="K47" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B48" s="85"/>
-      <c r="C48" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="G48" s="62"/>
-      <c r="I48" s="61" t="s">
-        <v>44</v>
-      </c>
-      <c r="J48" s="61"/>
-      <c r="K48" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
+      <c r="G43" s="53"/>
+      <c r="I43" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="J43" s="54"/>
+      <c r="K43" s="19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B44" s="89"/>
+      <c r="C44" s="86" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" s="86"/>
+      <c r="E44" s="86"/>
+      <c r="F44" s="90" t="s">
+        <v>78</v>
+      </c>
+      <c r="G44" s="90"/>
+      <c r="I44" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="J44" s="86"/>
+      <c r="K44" s="87" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" ht="18" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <mergeCells count="103">
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="C43:E43"/>
+  <mergeCells count="91">
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="I43:J43"/>
-    <mergeCell ref="B39:B43"/>
     <mergeCell ref="C39:E39"/>
     <mergeCell ref="F39:G39"/>
     <mergeCell ref="I39:J39"/>
     <mergeCell ref="C40:E40"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="I40:J40"/>
-    <mergeCell ref="B45:B48"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="B42:B44"/>
     <mergeCell ref="C42:E42"/>
     <mergeCell ref="F42:G42"/>
     <mergeCell ref="I42:J42"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="B32:B37"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="B32:B35"/>
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="I32:J32"/>
@@ -2157,17 +2187,28 @@
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="I34:J34"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="C22:E22"/>
     <mergeCell ref="B25:B30"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="I25:I30"/>
     <mergeCell ref="J25:K25"/>
     <mergeCell ref="C26:H30"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="I23:J23"/>
     <mergeCell ref="B16:B23"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="F16:G16"/>
@@ -2177,13 +2218,6 @@
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="C22:E22"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="C19:E19"/>
@@ -2192,21 +2226,11 @@
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:I12"/>
-    <mergeCell ref="J12:J14"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:I14"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:K9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:I10"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:H4"/>
@@ -2215,6 +2239,12 @@
     <mergeCell ref="E6:I6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:I7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:K9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:I10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
